--- a/myprojects/GatiGo/BvsA/GatiGo_Q1_Budget.xlsx
+++ b/myprojects/GatiGo/BvsA/GatiGo_Q1_Budget.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\GitHub\inakm.github.io\myprojects\GatiGo\BvsA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="900" windowWidth="28800" windowHeight="13860" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="450" windowWidth="28800" windowHeight="13860" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Budget Assumptions" sheetId="1" r:id="rId1"/>
@@ -533,9 +533,6 @@
     <t>Fixed OpEx + D&amp;A + Interest</t>
   </si>
   <si>
-    <t>GatiGo — Actual vs. Budget Analysis Template  |  Q1 FY2026</t>
-  </si>
-  <si>
     <t>Jan Actual</t>
   </si>
   <si>
@@ -591,6 +588,9 @@
   </si>
   <si>
     <t>BUDGET file — set before Q1 commenced. Compare against Actual for variance analysis. Blue = hardcoded input | Yellow = key assumption | Green text = cross-sheet link</t>
+  </si>
+  <si>
+    <t>GatiGo - Actual vs. Budget Analysis  |  Q1 of FY2026</t>
   </si>
 </sst>
 </file>
@@ -1271,30 +1271,37 @@
     <xf numFmtId="0" fontId="24" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1305,13 +1312,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1589,26 +1589,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="113" t="s">
-        <v>189</v>
-      </c>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
+      <c r="A2" s="109" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
     </row>
     <row r="3" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1634,15 +1634,15 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="109" t="s">
+      <c r="A4" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1832,15 +1832,15 @@
       <c r="I12" s="104"/>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="109" t="s">
+      <c r="A13" s="111" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="109"/>
-      <c r="C13" s="109"/>
-      <c r="D13" s="109"/>
-      <c r="E13" s="109"/>
-      <c r="F13" s="109"/>
-      <c r="G13" s="109"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="111"/>
+      <c r="G13" s="111"/>
       <c r="I13" s="104"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1940,15 +1940,15 @@
       <c r="I17" s="104"/>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="109" t="s">
+      <c r="A18" s="111" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="109"/>
-      <c r="D18" s="109"/>
-      <c r="E18" s="109"/>
-      <c r="F18" s="109"/>
-      <c r="G18" s="109"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="111"/>
       <c r="I18" s="104"/>
     </row>
     <row r="19" spans="1:9" ht="24" x14ac:dyDescent="0.25">
@@ -2048,15 +2048,15 @@
       <c r="I22" s="104"/>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="111" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="109"/>
-      <c r="C23" s="109"/>
-      <c r="D23" s="109"/>
-      <c r="E23" s="109"/>
-      <c r="F23" s="109"/>
-      <c r="G23" s="109"/>
+      <c r="B23" s="111"/>
+      <c r="C23" s="111"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="111"/>
+      <c r="F23" s="111"/>
+      <c r="G23" s="111"/>
       <c r="I23" s="104"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -2317,15 +2317,15 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="109" t="s">
+      <c r="A35" s="111" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="109"/>
-      <c r="C35" s="109"/>
-      <c r="D35" s="109"/>
-      <c r="E35" s="109"/>
-      <c r="F35" s="109"/>
-      <c r="G35" s="109"/>
+      <c r="B35" s="111"/>
+      <c r="C35" s="111"/>
+      <c r="D35" s="111"/>
+      <c r="E35" s="111"/>
+      <c r="F35" s="111"/>
+      <c r="G35" s="111"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
@@ -2420,124 +2420,124 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="119"/>
-      <c r="B41" s="119"/>
-      <c r="C41" s="119"/>
-      <c r="D41" s="119"/>
-      <c r="E41" s="119"/>
-      <c r="F41" s="119"/>
-      <c r="G41" s="119"/>
-      <c r="H41" s="120"/>
+      <c r="A41" s="112"/>
+      <c r="B41" s="112"/>
+      <c r="C41" s="112"/>
+      <c r="D41" s="112"/>
+      <c r="E41" s="112"/>
+      <c r="F41" s="112"/>
+      <c r="G41" s="112"/>
+      <c r="H41" s="107"/>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="121"/>
-      <c r="B42" s="121"/>
-      <c r="C42" s="121"/>
-      <c r="D42" s="121"/>
-      <c r="E42" s="121"/>
-      <c r="F42" s="121"/>
-      <c r="G42" s="121"/>
-      <c r="H42" s="120"/>
+      <c r="A42" s="113"/>
+      <c r="B42" s="113"/>
+      <c r="C42" s="113"/>
+      <c r="D42" s="113"/>
+      <c r="E42" s="113"/>
+      <c r="F42" s="113"/>
+      <c r="G42" s="113"/>
+      <c r="H42" s="107"/>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="121"/>
-      <c r="B43" s="121"/>
-      <c r="C43" s="121"/>
-      <c r="D43" s="121"/>
-      <c r="E43" s="121"/>
-      <c r="F43" s="121"/>
-      <c r="G43" s="121"/>
-      <c r="H43" s="120"/>
+      <c r="A43" s="113"/>
+      <c r="B43" s="113"/>
+      <c r="C43" s="113"/>
+      <c r="D43" s="113"/>
+      <c r="E43" s="113"/>
+      <c r="F43" s="113"/>
+      <c r="G43" s="113"/>
+      <c r="H43" s="107"/>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="109" t="s">
+      <c r="A44" s="111" t="s">
         <v>106</v>
       </c>
-      <c r="B44" s="109"/>
-      <c r="C44" s="109"/>
-      <c r="D44" s="109"/>
-      <c r="E44" s="109"/>
-      <c r="F44" s="109"/>
-      <c r="G44" s="109"/>
-      <c r="H44" s="120"/>
+      <c r="B44" s="111"/>
+      <c r="C44" s="111"/>
+      <c r="D44" s="111"/>
+      <c r="E44" s="111"/>
+      <c r="F44" s="111"/>
+      <c r="G44" s="111"/>
+      <c r="H44" s="107"/>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="110" t="s">
+      <c r="A45" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="B45" s="110"/>
-      <c r="C45" s="110"/>
-      <c r="D45" s="110"/>
-      <c r="E45" s="110"/>
-      <c r="F45" s="110"/>
-      <c r="G45" s="110"/>
-      <c r="H45" s="120"/>
+      <c r="B45" s="116"/>
+      <c r="C45" s="116"/>
+      <c r="D45" s="116"/>
+      <c r="E45" s="116"/>
+      <c r="F45" s="116"/>
+      <c r="G45" s="116"/>
+      <c r="H45" s="107"/>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="111" t="s">
+      <c r="A46" s="117" t="s">
         <v>108</v>
       </c>
-      <c r="B46" s="111"/>
-      <c r="C46" s="111"/>
-      <c r="D46" s="111"/>
-      <c r="E46" s="111"/>
-      <c r="F46" s="111"/>
-      <c r="G46" s="111"/>
-      <c r="H46" s="120"/>
+      <c r="B46" s="117"/>
+      <c r="C46" s="117"/>
+      <c r="D46" s="117"/>
+      <c r="E46" s="117"/>
+      <c r="F46" s="117"/>
+      <c r="G46" s="117"/>
+      <c r="H46" s="107"/>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="107" t="s">
+      <c r="A47" s="114" t="s">
         <v>109</v>
       </c>
-      <c r="B47" s="107"/>
-      <c r="C47" s="107"/>
-      <c r="D47" s="107"/>
-      <c r="E47" s="107"/>
-      <c r="F47" s="107"/>
-      <c r="G47" s="107"/>
-      <c r="H47" s="120"/>
+      <c r="B47" s="114"/>
+      <c r="C47" s="114"/>
+      <c r="D47" s="114"/>
+      <c r="E47" s="114"/>
+      <c r="F47" s="114"/>
+      <c r="G47" s="114"/>
+      <c r="H47" s="107"/>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="108" t="s">
+      <c r="A48" s="115" t="s">
         <v>110</v>
       </c>
-      <c r="B48" s="108"/>
-      <c r="C48" s="108"/>
-      <c r="D48" s="108"/>
-      <c r="E48" s="108"/>
-      <c r="F48" s="108"/>
-      <c r="G48" s="108"/>
-      <c r="H48" s="120"/>
+      <c r="B48" s="115"/>
+      <c r="C48" s="115"/>
+      <c r="D48" s="115"/>
+      <c r="E48" s="115"/>
+      <c r="F48" s="115"/>
+      <c r="G48" s="115"/>
+      <c r="H48" s="107"/>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="121"/>
-      <c r="B49" s="121"/>
-      <c r="C49" s="121"/>
-      <c r="D49" s="121"/>
-      <c r="E49" s="121"/>
-      <c r="F49" s="121"/>
-      <c r="G49" s="121"/>
-      <c r="H49" s="120"/>
+      <c r="A49" s="113"/>
+      <c r="B49" s="113"/>
+      <c r="C49" s="113"/>
+      <c r="D49" s="113"/>
+      <c r="E49" s="113"/>
+      <c r="F49" s="113"/>
+      <c r="G49" s="113"/>
+      <c r="H49" s="107"/>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="121"/>
-      <c r="B50" s="121"/>
-      <c r="C50" s="121"/>
-      <c r="D50" s="121"/>
-      <c r="E50" s="121"/>
-      <c r="F50" s="121"/>
-      <c r="G50" s="121"/>
-      <c r="H50" s="120"/>
+      <c r="A50" s="113"/>
+      <c r="B50" s="113"/>
+      <c r="C50" s="113"/>
+      <c r="D50" s="113"/>
+      <c r="E50" s="113"/>
+      <c r="F50" s="113"/>
+      <c r="G50" s="113"/>
+      <c r="H50" s="107"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="120"/>
-      <c r="B51" s="120"/>
-      <c r="C51" s="120"/>
-      <c r="D51" s="120"/>
-      <c r="E51" s="120"/>
-      <c r="F51" s="120"/>
-      <c r="G51" s="120"/>
-      <c r="H51" s="120"/>
+      <c r="A51" s="107"/>
+      <c r="B51" s="107"/>
+      <c r="C51" s="107"/>
+      <c r="D51" s="107"/>
+      <c r="E51" s="107"/>
+      <c r="F51" s="107"/>
+      <c r="G51" s="107"/>
+      <c r="H51" s="107"/>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2546,16 +2546,6 @@
     <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A47:G47"/>
     <mergeCell ref="A48:G48"/>
     <mergeCell ref="A49:G49"/>
@@ -2563,6 +2553,16 @@
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A45:G45"/>
     <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A18:G18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2581,28 +2581,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="108" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="113" t="s">
-        <v>188</v>
-      </c>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
+      <c r="A2" s="109" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
     </row>
     <row r="3" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -2631,16 +2631,16 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="109" t="s">
+      <c r="A4" s="111" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -2854,16 +2854,16 @@
       <c r="H13" s="14"/>
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="109" t="s">
+      <c r="A14" s="111" t="s">
         <v>129</v>
       </c>
-      <c r="B14" s="109"/>
-      <c r="C14" s="109"/>
-      <c r="D14" s="109"/>
-      <c r="E14" s="109"/>
-      <c r="F14" s="109"/>
-      <c r="G14" s="109"/>
-      <c r="H14" s="109"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
@@ -3051,16 +3051,16 @@
       <c r="H21" s="14"/>
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="109" t="s">
+      <c r="A22" s="111" t="s">
         <v>135</v>
       </c>
-      <c r="B22" s="109"/>
-      <c r="C22" s="109"/>
-      <c r="D22" s="109"/>
-      <c r="E22" s="109"/>
-      <c r="F22" s="109"/>
-      <c r="G22" s="109"/>
-      <c r="H22" s="109"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="111"/>
+      <c r="G22" s="111"/>
+      <c r="H22" s="111"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
@@ -3512,16 +3512,16 @@
       <c r="H37" s="14"/>
     </row>
     <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="109" t="s">
+      <c r="A38" s="111" t="s">
         <v>149</v>
       </c>
-      <c r="B38" s="109"/>
-      <c r="C38" s="109"/>
-      <c r="D38" s="109"/>
-      <c r="E38" s="109"/>
-      <c r="F38" s="109"/>
-      <c r="G38" s="109"/>
-      <c r="H38" s="109"/>
+      <c r="B38" s="111"/>
+      <c r="C38" s="111"/>
+      <c r="D38" s="111"/>
+      <c r="E38" s="111"/>
+      <c r="F38" s="111"/>
+      <c r="G38" s="111"/>
+      <c r="H38" s="111"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
@@ -3759,16 +3759,16 @@
       <c r="H48" s="14"/>
     </row>
     <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="109" t="s">
+      <c r="A49" s="111" t="s">
         <v>157</v>
       </c>
-      <c r="B49" s="109"/>
-      <c r="C49" s="109"/>
-      <c r="D49" s="109"/>
-      <c r="E49" s="109"/>
-      <c r="F49" s="109"/>
-      <c r="G49" s="109"/>
-      <c r="H49" s="109"/>
+      <c r="B49" s="111"/>
+      <c r="C49" s="111"/>
+      <c r="D49" s="111"/>
+      <c r="E49" s="111"/>
+      <c r="F49" s="111"/>
+      <c r="G49" s="111"/>
+      <c r="H49" s="111"/>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
@@ -3786,12 +3786,12 @@
         <f>IF(D12=0,"-",D20/D12)</f>
         <v>8.1731533343437329E-2</v>
       </c>
-      <c r="E50" s="115" t="s">
+      <c r="E50" s="118" t="s">
         <v>159</v>
       </c>
-      <c r="F50" s="115"/>
-      <c r="G50" s="115"/>
-      <c r="H50" s="115"/>
+      <c r="F50" s="118"/>
+      <c r="G50" s="118"/>
+      <c r="H50" s="118"/>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
@@ -3809,12 +3809,12 @@
         <f>IF(D12=0,"-",D36/D12)</f>
         <v>-0.91037959018258408</v>
       </c>
-      <c r="E51" s="115" t="s">
+      <c r="E51" s="118" t="s">
         <v>161</v>
       </c>
-      <c r="F51" s="115"/>
-      <c r="G51" s="115"/>
-      <c r="H51" s="115"/>
+      <c r="F51" s="118"/>
+      <c r="G51" s="118"/>
+      <c r="H51" s="118"/>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
@@ -3832,12 +3832,12 @@
         <f>IF(D12=0,"-",D47/D12)</f>
         <v>-0.94519050679753214</v>
       </c>
-      <c r="E52" s="115" t="s">
+      <c r="E52" s="118" t="s">
         <v>163</v>
       </c>
-      <c r="F52" s="115"/>
-      <c r="G52" s="115"/>
-      <c r="H52" s="115"/>
+      <c r="F52" s="118"/>
+      <c r="G52" s="118"/>
+      <c r="H52" s="118"/>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
@@ -3855,12 +3855,12 @@
         <f>IF(D5=0,"-",D12/D5)</f>
         <v>65.473779516152391</v>
       </c>
-      <c r="E53" s="115" t="s">
+      <c r="E53" s="118" t="s">
         <v>165</v>
       </c>
-      <c r="F53" s="115"/>
-      <c r="G53" s="115"/>
-      <c r="H53" s="115"/>
+      <c r="F53" s="118"/>
+      <c r="G53" s="118"/>
+      <c r="H53" s="118"/>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
@@ -3878,12 +3878,12 @@
         <f>IF(D5=0,"-",(D12-D18)/D5)</f>
         <v>5.3512723936452735</v>
       </c>
-      <c r="E54" s="115" t="s">
+      <c r="E54" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="F54" s="115"/>
-      <c r="G54" s="115"/>
-      <c r="H54" s="115"/>
+      <c r="F54" s="118"/>
+      <c r="G54" s="118"/>
+      <c r="H54" s="118"/>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
@@ -3901,20 +3901,15 @@
         <f>D34+D39+D40</f>
         <v>472000</v>
       </c>
-      <c r="E55" s="115" t="s">
+      <c r="E55" s="118" t="s">
         <v>169</v>
       </c>
-      <c r="F55" s="115"/>
-      <c r="G55" s="115"/>
-      <c r="H55" s="115"/>
+      <c r="F55" s="118"/>
+      <c r="G55" s="118"/>
+      <c r="H55" s="118"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A22:H22"/>
     <mergeCell ref="E53:H53"/>
     <mergeCell ref="E54:H54"/>
     <mergeCell ref="E55:H55"/>
@@ -3923,6 +3918,11 @@
     <mergeCell ref="E50:H50"/>
     <mergeCell ref="E51:H51"/>
     <mergeCell ref="E52:H52"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3941,92 +3941,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="117" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
+      <c r="A1" s="120" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="114"/>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
+      <c r="A2" s="110"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="110"/>
     </row>
     <row r="3" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="44" t="s">
         <v>112</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>113</v>
       </c>
       <c r="D3" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="E3" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="F3" s="44" t="s">
         <v>173</v>
-      </c>
-      <c r="F3" s="44" t="s">
-        <v>174</v>
       </c>
       <c r="G3" s="44" t="s">
         <v>116</v>
       </c>
       <c r="H3" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="I3" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="I3" s="44" t="s">
+      <c r="J3" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="J3" s="44" t="s">
-        <v>177</v>
-      </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="118"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="121"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="119" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="116"/>
+      <c r="B5" s="119"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B6" s="74">
         <v>89237.288135593204</v>
@@ -4059,7 +4059,7 @@
         <v>-0.13797514619883144</v>
       </c>
       <c r="J6" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -4067,7 +4067,7 @@
         <v>124</v>
       </c>
       <c r="B7" s="75" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C7" s="15">
         <f>'Budget P&amp;L - Q1 FY2026'!B8</f>
@@ -4097,12 +4097,12 @@
         <v>-0.33333333333333331</v>
       </c>
       <c r="J7" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B8" s="74">
         <v>86400</v>
@@ -4135,7 +4135,7 @@
         <v>-0.15789473684210525</v>
       </c>
       <c r="J8" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -4173,7 +4173,7 @@
         <v>-0.22222222222222221</v>
       </c>
       <c r="J9" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -4211,7 +4211,7 @@
         <v>-0.29411764705882354</v>
       </c>
       <c r="J10" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4251,22 +4251,22 @@
         <v>-0.1800039838801466</v>
       </c>
       <c r="J11" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="116" t="s">
+      <c r="A12" s="119" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="116"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="116"/>
-      <c r="E12" s="116"/>
-      <c r="F12" s="116"/>
-      <c r="G12" s="116"/>
-      <c r="H12" s="116"/>
-      <c r="I12" s="116"/>
-      <c r="J12" s="116"/>
+      <c r="B12" s="119"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="119"/>
+      <c r="H12" s="119"/>
+      <c r="I12" s="119"/>
+      <c r="J12" s="119"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
@@ -4303,7 +4303,7 @@
         <v>0.16552631578947369</v>
       </c>
       <c r="J13" s="52" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -4341,7 +4341,7 @@
         <v>0.15241228070175439</v>
       </c>
       <c r="J14" s="52" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -4379,7 +4379,7 @@
         <v>0.18823529411764706</v>
       </c>
       <c r="J15" s="52" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4417,7 +4417,7 @@
         <v>0.16751658715797554</v>
       </c>
       <c r="J16" s="56" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4469,22 +4469,22 @@
         <v>-0.57144730005973343</v>
       </c>
       <c r="J18" s="76" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="116" t="s">
+      <c r="A19" s="119" t="s">
         <v>135</v>
       </c>
-      <c r="B19" s="116"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="116"/>
-      <c r="I19" s="116"/>
-      <c r="J19" s="116"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="119"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="119"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
@@ -4521,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="79" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="79" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -4597,7 +4597,7 @@
         <v>-8.3333333333333329E-2</v>
       </c>
       <c r="J22" s="79" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -4635,12 +4635,12 @@
         <v>-0.27777777777777779</v>
       </c>
       <c r="J23" s="79" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B24" s="84">
         <v>25000</v>
@@ -4673,12 +4673,12 @@
         <v>0</v>
       </c>
       <c r="J24" s="79" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B25" s="85">
         <v>80000</v>
@@ -4711,7 +4711,7 @@
         <v>-0.2</v>
       </c>
       <c r="J25" s="79" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -4749,7 +4749,7 @@
         <v>-0.6216216216216216</v>
       </c>
       <c r="J26" s="79" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -4787,7 +4787,7 @@
         <v>-0.14814814814814814</v>
       </c>
       <c r="J27" s="79" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="79" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -4863,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="79" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -4901,7 +4901,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="79" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4941,7 +4941,7 @@
         <v>-8.6245353159851296E-2</v>
       </c>
       <c r="J31" s="76" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4958,7 +4958,7 @@
     </row>
     <row r="33" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="59" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B33" s="47">
         <f>B18-B31</f>
@@ -4993,12 +4993,12 @@
         <v>-0.10376915813091903</v>
       </c>
       <c r="J33" s="102" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B35" s="103">
         <v>16000</v>
@@ -5031,7 +5031,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="106" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -5048,7 +5048,7 @@
     </row>
     <row r="37" spans="1:10" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="64" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B37" s="47">
         <f>B33-B35</f>
@@ -5083,7 +5083,7 @@
         <v>-0.10010157560118907</v>
       </c>
       <c r="J37" s="105" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
